--- a/01_プロジェクト/BUYMA購入者配布資料/BUYMA_直営店連携確認台帳_購入者版.xlsx
+++ b/01_プロジェクト/BUYMA購入者配布資料/BUYMA_直営店連携確認台帳_購入者版.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="直営店確認台帳" sheetId="1" r:id="Rc5ae6416587640fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使い方" sheetId="2" r:id="R2e31bb692c3e4543"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="問い合わせ記録" sheetId="3" r:id="Rf8aa02f44b5549b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="直営店確認台帳" sheetId="1" r:id="R59b4717e16c94714"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使い方" sheetId="2" r:id="Rd1718f031426427b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="問い合わせ記録" sheetId="3" r:id="R4577281c2c294dc3"/>
   </x:sheets>
 </x:workbook>
 </file>
